--- a/formularios/Lista de Empleados.xlsx
+++ b/formularios/Lista de Empleados.xlsx
@@ -1,26 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Documentos\proyectos\Agente-IA-360\formularios\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{520B3029-F55E-49C1-8555-4D34BBC9903E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7545" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
-    <sheet name="Empleados" sheetId="1" r:id="rId1"/>
+    <sheet state="visible" name="Empleados" sheetId="1" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <definedNames/>
+  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="37">
   <si>
     <t>Nombre</t>
   </si>
@@ -46,105 +37,136 @@
     <t>Correo</t>
   </si>
   <si>
-    <t>Julio</t>
-  </si>
-  <si>
-    <t>Soria</t>
+    <t>Tom</t>
+  </si>
+  <si>
+    <t>Hanks</t>
+  </si>
+  <si>
+    <t>Operador</t>
+  </si>
+  <si>
+    <t>parra.jesus@gmail.com</t>
+  </si>
+  <si>
+    <t>Meryl</t>
+  </si>
+  <si>
+    <t>Streep</t>
+  </si>
+  <si>
+    <t>Secretaria</t>
+  </si>
+  <si>
+    <t>Leonardo</t>
+  </si>
+  <si>
+    <t>DiCaprio</t>
+  </si>
+  <si>
+    <t>Scarlett</t>
+  </si>
+  <si>
+    <t>Johansson</t>
+  </si>
+  <si>
+    <t>Robert</t>
+  </si>
+  <si>
+    <t>De Niro</t>
+  </si>
+  <si>
+    <t>Viola</t>
+  </si>
+  <si>
+    <t>Davis</t>
+  </si>
+  <si>
+    <t>Brad</t>
+  </si>
+  <si>
+    <t>Pitt</t>
+  </si>
+  <si>
+    <t>Natalie</t>
+  </si>
+  <si>
+    <t>Portman</t>
+  </si>
+  <si>
+    <t>Denzel</t>
+  </si>
+  <si>
+    <t>Washington</t>
+  </si>
+  <si>
+    <t>Cate</t>
+  </si>
+  <si>
+    <t>Blanchett</t>
+  </si>
+  <si>
+    <t>Jesus</t>
+  </si>
+  <si>
+    <t>Parra</t>
+  </si>
+  <si>
+    <t>Asesor</t>
+  </si>
+  <si>
+    <t>Eusebio</t>
+  </si>
+  <si>
+    <t>Pernia</t>
   </si>
   <si>
     <t>Supervisor</t>
-  </si>
-  <si>
-    <t>Christian</t>
-  </si>
-  <si>
-    <t>Aragon</t>
-  </si>
-  <si>
-    <t>Asesor</t>
-  </si>
-  <si>
-    <t>Jorge</t>
-  </si>
-  <si>
-    <t>Starper</t>
-  </si>
-  <si>
-    <t>Operador</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carlos </t>
-  </si>
-  <si>
-    <t>Chavez</t>
-  </si>
-  <si>
-    <t>Ana</t>
-  </si>
-  <si>
-    <t>Cordoba</t>
-  </si>
-  <si>
-    <t>Coordinador</t>
-  </si>
-  <si>
-    <t>Rosa</t>
-  </si>
-  <si>
-    <t>Perez</t>
-  </si>
-  <si>
-    <t>Secretaria</t>
-  </si>
-  <si>
-    <t>parra.jesus@gmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
       <color rgb="FF1F1F1F"/>
       <name val="Google Sans Text"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10"/>
       <color theme="1"/>
       <name val="Google Sans Text"/>
     </font>
     <font>
-      <sz val="10"/>
       <color rgb="FF1F1F1F"/>
       <name val="Google Sans Text"/>
     </font>
     <font>
-      <u/>
-      <sz val="10"/>
-      <color theme="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
@@ -154,61 +176,74 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
   </fills>
   <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
   </borders>
-  <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+  <cellStyleXfs count="1">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="12">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
+  <cellXfs count="16">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="3" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="3" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="1">
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -216,7 +251,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -406,28 +441,25 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="2" width="7.5703125" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" customWidth="1"/>
-    <col min="7" max="7" width="6.5703125" customWidth="1"/>
-    <col min="8" max="8" width="27" bestFit="1" customWidth="1"/>
+    <col customWidth="1" min="1" max="2" width="7.63"/>
+    <col customWidth="1" min="3" max="3" width="15.75"/>
+    <col customWidth="1" min="5" max="5" width="20.5"/>
+    <col customWidth="1" min="6" max="6" width="14.88"/>
+    <col customWidth="1" min="7" max="7" width="6.63"/>
+    <col customWidth="1" min="8" max="8" width="24.25"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -453,197 +485,351 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2">
       <c r="A2" s="4" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="4" t="str">
-        <f t="shared" ref="C2:C7" si="0">CONCATENATE(A2," ",B2)</f>
-        <v>Julio Soria</v>
-      </c>
-      <c r="D2" s="5">
-        <v>30987456</v>
-      </c>
-      <c r="E2" s="6" t="s">
+      <c r="C2" s="5" t="str">
+        <f t="shared" ref="C2:C13" si="1">CONCATENATE(A2," ",B2)</f>
+        <v>Tom Hanks</v>
+      </c>
+      <c r="D2" s="6">
+        <v>3.0987456E7</v>
+      </c>
+      <c r="E2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="7">
-        <v>46032</v>
-      </c>
-      <c r="G2" s="8">
-        <v>2</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="F2" s="8">
+        <v>46032.0</v>
+      </c>
+      <c r="G2" s="9">
+        <v>1.0</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Christian Aragon</v>
-      </c>
-      <c r="D3" s="8">
-        <v>9456989</v>
-      </c>
-      <c r="E3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="9">
-        <v>46033</v>
-      </c>
-      <c r="G3" s="8">
-        <v>2</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="C3" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Meryl Streep</v>
+      </c>
+      <c r="D3" s="11">
+        <v>9456989.0</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="12">
+        <v>46033.0</v>
+      </c>
+      <c r="G3" s="9">
+        <v>1.0</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Jorge Starper</v>
-      </c>
-      <c r="D4" s="8">
-        <v>9751423</v>
-      </c>
-      <c r="E4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="9">
-        <v>46034</v>
-      </c>
-      <c r="G4" s="8">
-        <v>2</v>
-      </c>
-      <c r="H4" s="11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="C4" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Leonardo DiCaprio</v>
+      </c>
+      <c r="D4" s="11">
+        <v>9751423.0</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="12">
+        <v>46034.0</v>
+      </c>
+      <c r="G4" s="9">
+        <v>1.0</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" s="4" t="s">
         <v>17</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Carlos  Chavez</v>
-      </c>
-      <c r="D5" s="8">
-        <v>10365289</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" s="9">
-        <v>46035</v>
-      </c>
-      <c r="G5" s="8">
-        <v>2</v>
-      </c>
-      <c r="H5" s="11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="C5" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Scarlett Johansson</v>
+      </c>
+      <c r="D5" s="11">
+        <v>1.0365289E7</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="12">
+        <v>46035.0</v>
+      </c>
+      <c r="G5" s="9">
+        <v>1.0</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" s="4" t="s">
         <v>19</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Ana Cordoba</v>
-      </c>
-      <c r="D6" s="10">
-        <v>30111345</v>
-      </c>
-      <c r="E6" s="4" t="s">
+      <c r="C6" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Robert De Niro</v>
+      </c>
+      <c r="D6" s="13">
+        <v>3.0222345E7</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="8">
+        <v>46023.0</v>
+      </c>
+      <c r="G6" s="11">
+        <v>1.0</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="F6" s="7">
-        <v>46023</v>
-      </c>
-      <c r="G6" s="8">
-        <v>1</v>
-      </c>
-      <c r="H6" s="11" t="s">
+      <c r="B7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Viola Davis</v>
+      </c>
+      <c r="D7" s="9">
+        <v>2.1997425E7</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="8">
+        <v>46065.0</v>
+      </c>
+      <c r="G7" s="11">
+        <v>1.0</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Brad Pitt</v>
+      </c>
+      <c r="D8" s="9">
+        <v>9646989.0</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="12">
+        <v>46033.0</v>
+      </c>
+      <c r="G8" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>Rosa Perez</v>
-      </c>
-      <c r="D7" s="8">
-        <v>21897425</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F7" s="7">
-        <v>46065</v>
-      </c>
-      <c r="G7" s="8">
-        <v>1</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
+      <c r="B9" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Natalie Portman</v>
+      </c>
+      <c r="D9" s="9">
+        <v>9781423.0</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="12">
+        <v>46034.0</v>
+      </c>
+      <c r="G9" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Denzel Washington</v>
+      </c>
+      <c r="D10" s="9">
+        <v>1.1365289E7</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" s="12">
+        <v>46035.0</v>
+      </c>
+      <c r="G10" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Cate Blanchett</v>
+      </c>
+      <c r="D11" s="9">
+        <v>9556989.0</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="8">
+        <v>46023.0</v>
+      </c>
+      <c r="G11" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Jesus Parra</v>
+      </c>
+      <c r="D12" s="9">
+        <v>1.1445665E7</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" s="15">
+        <v>44562.0</v>
+      </c>
+      <c r="G12" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>11</v>
+      </c>
       <c r="K12" s="1"/>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13">
+      <c r="A13" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Eusebio Pernia</v>
+      </c>
+      <c r="D13" s="9">
+        <v>1.1878453E7</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="F13" s="15">
+        <v>44562.0</v>
+      </c>
+      <c r="G13" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>11</v>
+      </c>
       <c r="K13" s="1"/>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14">
       <c r="K14" s="2"/>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15">
       <c r="K15" s="1"/>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16">
       <c r="K16" s="1"/>
     </row>
-    <row r="17" spans="11:11">
+    <row r="17">
       <c r="K17" s="1"/>
     </row>
-    <row r="18" spans="11:11">
+    <row r="18">
       <c r="K18" s="2"/>
     </row>
-    <row r="19" spans="11:11">
+    <row r="19">
       <c r="K19" s="3"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="H2" r:id="rId1" xr:uid="{78D5B88E-7402-4811-921C-054F584AB0C6}"/>
-    <hyperlink ref="H3:H7" r:id="rId2" display="parra.jesus@gmail.com" xr:uid="{1A6B19CC-35B5-482A-B562-35356D318DF5}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>